--- a/artfynd/A 58513-2025 artfynd.xlsx
+++ b/artfynd/A 58513-2025 artfynd.xlsx
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>132795978</v>
+        <v>132795817</v>
       </c>
       <c r="B3" t="n">
-        <v>79333</v>
+        <v>57955</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -798,34 +798,39 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Saxberget, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>497639</v>
+        <v>497613</v>
       </c>
       <c r="R3" t="n">
-        <v>6666288</v>
+        <v>6666353</v>
       </c>
       <c r="S3" t="n">
         <v>1</v>
@@ -857,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:35</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -867,7 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:35</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -894,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>132795817</v>
+        <v>132795978</v>
       </c>
       <c r="B4" t="n">
-        <v>57955</v>
+        <v>79333</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -905,39 +910,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Saxberget, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>497613</v>
+        <v>497639</v>
       </c>
       <c r="R4" t="n">
-        <v>6666353</v>
+        <v>6666288</v>
       </c>
       <c r="S4" t="n">
         <v>1</v>
@@ -969,7 +969,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1347,45 +1347,50 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>132792240</v>
+        <v>132795456</v>
       </c>
       <c r="B8" t="n">
-        <v>91291</v>
+        <v>57955</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5685</v>
+        <v>100049</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Gullgröppa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Pseudomerulius aureus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Jülich</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Saxberget, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>497881</v>
+        <v>497730</v>
       </c>
       <c r="R8" t="n">
-        <v>6666310</v>
+        <v>6666268</v>
       </c>
       <c r="S8" t="n">
         <v>1</v>
@@ -1417,7 +1422,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1427,7 +1432,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1454,50 +1459,45 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>132795456</v>
+        <v>132792240</v>
       </c>
       <c r="B9" t="n">
-        <v>57955</v>
+        <v>91291</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100049</v>
+        <v>5685</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Gullgröppa</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Pseudomerulius aureus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Jülich</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Saxberget, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>497730</v>
+        <v>497881</v>
       </c>
       <c r="R9" t="n">
-        <v>6666268</v>
+        <v>6666310</v>
       </c>
       <c r="S9" t="n">
         <v>1</v>
@@ -1529,7 +1529,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1539,7 +1539,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -2574,10 +2574,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>132793510</v>
+        <v>132792291</v>
       </c>
       <c r="B19" t="n">
-        <v>57958</v>
+        <v>57955</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2585,16 +2585,16 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -2614,13 +2614,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>497770</v>
+        <v>497918</v>
       </c>
       <c r="R19" t="n">
-        <v>6666395</v>
+        <v>6666359</v>
       </c>
       <c r="S19" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2649,7 +2649,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2659,7 +2659,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2686,10 +2686,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>132792291</v>
+        <v>132793510</v>
       </c>
       <c r="B20" t="n">
-        <v>57955</v>
+        <v>57958</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2697,16 +2697,16 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -2726,13 +2726,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>497918</v>
+        <v>497770</v>
       </c>
       <c r="R20" t="n">
-        <v>6666359</v>
+        <v>6666395</v>
       </c>
       <c r="S20" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2761,7 +2761,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2771,7 +2771,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AD20" t="b">

--- a/artfynd/A 58513-2025 artfynd.xlsx
+++ b/artfynd/A 58513-2025 artfynd.xlsx
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>132795817</v>
+        <v>132795978</v>
       </c>
       <c r="B3" t="n">
-        <v>57955</v>
+        <v>79333</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -798,39 +798,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Saxberget, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>497613</v>
+        <v>497639</v>
       </c>
       <c r="R3" t="n">
-        <v>6666353</v>
+        <v>6666288</v>
       </c>
       <c r="S3" t="n">
         <v>1</v>
@@ -862,7 +857,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +867,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,10 +894,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>132795978</v>
+        <v>132795817</v>
       </c>
       <c r="B4" t="n">
-        <v>79333</v>
+        <v>57955</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -910,34 +905,39 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Saxberget, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>497639</v>
+        <v>497613</v>
       </c>
       <c r="R4" t="n">
-        <v>6666288</v>
+        <v>6666353</v>
       </c>
       <c r="S4" t="n">
         <v>1</v>
@@ -969,7 +969,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:35</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:35</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1347,50 +1347,45 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>132795456</v>
+        <v>132792240</v>
       </c>
       <c r="B8" t="n">
-        <v>57955</v>
+        <v>91291</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100049</v>
+        <v>5685</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Gullgröppa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Pseudomerulius aureus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Jülich</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Saxberget, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>497730</v>
+        <v>497881</v>
       </c>
       <c r="R8" t="n">
-        <v>6666268</v>
+        <v>6666310</v>
       </c>
       <c r="S8" t="n">
         <v>1</v>
@@ -1422,7 +1417,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1432,7 +1427,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1459,45 +1454,50 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>132792240</v>
+        <v>132795456</v>
       </c>
       <c r="B9" t="n">
-        <v>91291</v>
+        <v>57955</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5685</v>
+        <v>100049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Gullgröppa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Pseudomerulius aureus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Jülich</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Saxberget, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>497881</v>
+        <v>497730</v>
       </c>
       <c r="R9" t="n">
-        <v>6666310</v>
+        <v>6666268</v>
       </c>
       <c r="S9" t="n">
         <v>1</v>
@@ -1529,7 +1529,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1539,7 +1539,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1902,7 +1902,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>132792691</v>
+        <v>132794362</v>
       </c>
       <c r="B13" t="n">
         <v>57955</v>
@@ -1933,7 +1933,7 @@
       <c r="I13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
-          <t>besöker bebott bo</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -1942,10 +1942,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>497882</v>
+        <v>497703</v>
       </c>
       <c r="R13" t="n">
-        <v>6666359</v>
+        <v>6666468</v>
       </c>
       <c r="S13" t="n">
         <v>1</v>
@@ -1977,7 +1977,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>10:07</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1987,7 +1987,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>10:07</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2014,7 +2014,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>132794362</v>
+        <v>132792691</v>
       </c>
       <c r="B14" t="n">
         <v>57955</v>
@@ -2045,7 +2045,7 @@
       <c r="I14" t="inlineStr"/>
       <c r="M14" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>besöker bebott bo</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -2054,10 +2054,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>497703</v>
+        <v>497882</v>
       </c>
       <c r="R14" t="n">
-        <v>6666468</v>
+        <v>6666359</v>
       </c>
       <c r="S14" t="n">
         <v>1</v>
@@ -2089,7 +2089,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>10:07</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2099,7 +2099,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>10:07</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2238,7 +2238,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>132792333</v>
+        <v>132794021</v>
       </c>
       <c r="B16" t="n">
         <v>57955</v>
@@ -2269,7 +2269,7 @@
       <c r="I16" t="inlineStr"/>
       <c r="M16" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -2278,13 +2278,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>497895</v>
+        <v>497625</v>
       </c>
       <c r="R16" t="n">
-        <v>6666323</v>
+        <v>6666407</v>
       </c>
       <c r="S16" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2313,7 +2313,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>09:53</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2323,7 +2323,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>09:53</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2350,7 +2350,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>132794021</v>
+        <v>132792333</v>
       </c>
       <c r="B17" t="n">
         <v>57955</v>
@@ -2381,7 +2381,7 @@
       <c r="I17" t="inlineStr"/>
       <c r="M17" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -2390,13 +2390,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>497625</v>
+        <v>497895</v>
       </c>
       <c r="R17" t="n">
-        <v>6666407</v>
+        <v>6666323</v>
       </c>
       <c r="S17" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2425,7 +2425,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>09:53</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2435,7 +2435,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>09:53</t>
         </is>
       </c>
       <c r="AD17" t="b">

--- a/artfynd/A 58513-2025 artfynd.xlsx
+++ b/artfynd/A 58513-2025 artfynd.xlsx
@@ -1902,7 +1902,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>132794362</v>
+        <v>132792691</v>
       </c>
       <c r="B13" t="n">
         <v>57955</v>
@@ -1933,7 +1933,7 @@
       <c r="I13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>besöker bebott bo</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -1942,10 +1942,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>497703</v>
+        <v>497882</v>
       </c>
       <c r="R13" t="n">
-        <v>6666468</v>
+        <v>6666359</v>
       </c>
       <c r="S13" t="n">
         <v>1</v>
@@ -1977,7 +1977,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>10:07</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1987,7 +1987,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>10:07</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2014,7 +2014,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>132792691</v>
+        <v>132794362</v>
       </c>
       <c r="B14" t="n">
         <v>57955</v>
@@ -2045,7 +2045,7 @@
       <c r="I14" t="inlineStr"/>
       <c r="M14" t="inlineStr">
         <is>
-          <t>besöker bebott bo</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -2054,10 +2054,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>497882</v>
+        <v>497703</v>
       </c>
       <c r="R14" t="n">
-        <v>6666359</v>
+        <v>6666468</v>
       </c>
       <c r="S14" t="n">
         <v>1</v>
@@ -2089,7 +2089,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>10:07</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2099,7 +2099,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>10:07</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2238,7 +2238,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>132794021</v>
+        <v>132792333</v>
       </c>
       <c r="B16" t="n">
         <v>57955</v>
@@ -2269,7 +2269,7 @@
       <c r="I16" t="inlineStr"/>
       <c r="M16" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -2278,13 +2278,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>497625</v>
+        <v>497895</v>
       </c>
       <c r="R16" t="n">
-        <v>6666407</v>
+        <v>6666323</v>
       </c>
       <c r="S16" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2313,7 +2313,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>09:53</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2323,7 +2323,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>09:53</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2350,7 +2350,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>132792333</v>
+        <v>132794021</v>
       </c>
       <c r="B17" t="n">
         <v>57955</v>
@@ -2381,7 +2381,7 @@
       <c r="I17" t="inlineStr"/>
       <c r="M17" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -2390,13 +2390,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>497895</v>
+        <v>497625</v>
       </c>
       <c r="R17" t="n">
-        <v>6666323</v>
+        <v>6666407</v>
       </c>
       <c r="S17" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2425,7 +2425,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>09:53</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2435,7 +2435,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>09:53</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AD17" t="b">

--- a/artfynd/A 58513-2025 artfynd.xlsx
+++ b/artfynd/A 58513-2025 artfynd.xlsx
@@ -1347,45 +1347,50 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>132792240</v>
+        <v>132795456</v>
       </c>
       <c r="B8" t="n">
-        <v>91291</v>
+        <v>57955</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5685</v>
+        <v>100049</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Gullgröppa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Pseudomerulius aureus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Jülich</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Saxberget, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>497881</v>
+        <v>497730</v>
       </c>
       <c r="R8" t="n">
-        <v>6666310</v>
+        <v>6666268</v>
       </c>
       <c r="S8" t="n">
         <v>1</v>
@@ -1417,7 +1422,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1427,7 +1432,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1454,50 +1459,45 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>132795456</v>
+        <v>132792240</v>
       </c>
       <c r="B9" t="n">
-        <v>57955</v>
+        <v>91291</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100049</v>
+        <v>5685</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Gullgröppa</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Pseudomerulius aureus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Jülich</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Saxberget, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>497730</v>
+        <v>497881</v>
       </c>
       <c r="R9" t="n">
-        <v>6666268</v>
+        <v>6666310</v>
       </c>
       <c r="S9" t="n">
         <v>1</v>
@@ -1529,7 +1529,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1539,7 +1539,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1678,10 +1678,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>132792533</v>
+        <v>132792911</v>
       </c>
       <c r="B11" t="n">
-        <v>57955</v>
+        <v>57958</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1689,16 +1689,16 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1709,7 +1709,7 @@
       <c r="I11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1718,10 +1718,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>497914</v>
+        <v>497882</v>
       </c>
       <c r="R11" t="n">
-        <v>6666329</v>
+        <v>6666359</v>
       </c>
       <c r="S11" t="n">
         <v>1</v>
@@ -1753,7 +1753,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>10:02</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1763,14 +1763,14 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>10:02</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
       <c r="AE11" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG11" t="b">
         <v>0</v>
@@ -1790,10 +1790,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>132792911</v>
+        <v>132792533</v>
       </c>
       <c r="B12" t="n">
-        <v>57958</v>
+        <v>57955</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1801,16 +1801,16 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1821,7 +1821,7 @@
       <c r="I12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -1830,10 +1830,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>497882</v>
+        <v>497914</v>
       </c>
       <c r="R12" t="n">
-        <v>6666359</v>
+        <v>6666329</v>
       </c>
       <c r="S12" t="n">
         <v>1</v>
@@ -1865,7 +1865,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>10:02</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1875,14 +1875,14 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>10:02</t>
         </is>
       </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
       <c r="AE12" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG12" t="b">
         <v>0</v>

--- a/artfynd/A 58513-2025 artfynd.xlsx
+++ b/artfynd/A 58513-2025 artfynd.xlsx
@@ -2798,7 +2798,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>132793557</v>
+        <v>132793034</v>
       </c>
       <c r="B21" t="n">
         <v>57958</v>
@@ -2838,10 +2838,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>497804</v>
+        <v>497860</v>
       </c>
       <c r="R21" t="n">
-        <v>6666386</v>
+        <v>6666362</v>
       </c>
       <c r="S21" t="n">
         <v>1</v>
@@ -2873,7 +2873,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>10:18</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2883,14 +2883,14 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>10:18</t>
         </is>
       </c>
       <c r="AD21" t="b">
         <v>0</v>
       </c>
       <c r="AE21" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG21" t="b">
         <v>0</v>
@@ -2910,7 +2910,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>132793034</v>
+        <v>132793557</v>
       </c>
       <c r="B22" t="n">
         <v>57958</v>
@@ -2950,10 +2950,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>497860</v>
+        <v>497804</v>
       </c>
       <c r="R22" t="n">
-        <v>6666362</v>
+        <v>6666386</v>
       </c>
       <c r="S22" t="n">
         <v>1</v>
@@ -2985,7 +2985,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>10:18</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2995,14 +2995,14 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>10:18</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AD22" t="b">
         <v>0</v>
       </c>
       <c r="AE22" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG22" t="b">
         <v>0</v>

--- a/artfynd/A 58513-2025 artfynd.xlsx
+++ b/artfynd/A 58513-2025 artfynd.xlsx
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>132795978</v>
+        <v>132795817</v>
       </c>
       <c r="B3" t="n">
-        <v>79333</v>
+        <v>57955</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -798,34 +798,39 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Saxberget, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>497639</v>
+        <v>497613</v>
       </c>
       <c r="R3" t="n">
-        <v>6666288</v>
+        <v>6666353</v>
       </c>
       <c r="S3" t="n">
         <v>1</v>
@@ -857,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:35</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -867,7 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:35</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -894,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>132795817</v>
+        <v>132795978</v>
       </c>
       <c r="B4" t="n">
-        <v>57955</v>
+        <v>79333</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -905,39 +910,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Saxberget, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>497613</v>
+        <v>497639</v>
       </c>
       <c r="R4" t="n">
-        <v>6666353</v>
+        <v>6666288</v>
       </c>
       <c r="S4" t="n">
         <v>1</v>
@@ -969,7 +969,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1678,10 +1678,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>132792911</v>
+        <v>132792533</v>
       </c>
       <c r="B11" t="n">
-        <v>57958</v>
+        <v>57955</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1689,16 +1689,16 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1709,7 +1709,7 @@
       <c r="I11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1718,10 +1718,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>497882</v>
+        <v>497914</v>
       </c>
       <c r="R11" t="n">
-        <v>6666359</v>
+        <v>6666329</v>
       </c>
       <c r="S11" t="n">
         <v>1</v>
@@ -1753,7 +1753,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>10:02</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1763,14 +1763,14 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>10:02</t>
         </is>
       </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
       <c r="AE11" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG11" t="b">
         <v>0</v>
@@ -1790,10 +1790,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>132792533</v>
+        <v>132792911</v>
       </c>
       <c r="B12" t="n">
-        <v>57955</v>
+        <v>57958</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1801,16 +1801,16 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1821,7 +1821,7 @@
       <c r="I12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -1830,10 +1830,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>497914</v>
+        <v>497882</v>
       </c>
       <c r="R12" t="n">
-        <v>6666329</v>
+        <v>6666359</v>
       </c>
       <c r="S12" t="n">
         <v>1</v>
@@ -1865,7 +1865,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>10:02</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1875,14 +1875,14 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>10:02</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
       <c r="AE12" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG12" t="b">
         <v>0</v>
@@ -2574,10 +2574,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>132792291</v>
+        <v>132793510</v>
       </c>
       <c r="B19" t="n">
-        <v>57955</v>
+        <v>57958</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2585,16 +2585,16 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -2614,13 +2614,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>497918</v>
+        <v>497770</v>
       </c>
       <c r="R19" t="n">
-        <v>6666359</v>
+        <v>6666395</v>
       </c>
       <c r="S19" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2649,7 +2649,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2659,7 +2659,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2686,10 +2686,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>132793510</v>
+        <v>132792291</v>
       </c>
       <c r="B20" t="n">
-        <v>57958</v>
+        <v>57955</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2697,16 +2697,16 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -2726,13 +2726,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>497770</v>
+        <v>497918</v>
       </c>
       <c r="R20" t="n">
-        <v>6666395</v>
+        <v>6666359</v>
       </c>
       <c r="S20" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2761,7 +2761,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2771,7 +2771,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2798,7 +2798,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>132793034</v>
+        <v>132793557</v>
       </c>
       <c r="B21" t="n">
         <v>57958</v>
@@ -2838,10 +2838,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>497860</v>
+        <v>497804</v>
       </c>
       <c r="R21" t="n">
-        <v>6666362</v>
+        <v>6666386</v>
       </c>
       <c r="S21" t="n">
         <v>1</v>
@@ -2873,7 +2873,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>10:18</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2883,14 +2883,14 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>10:18</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AD21" t="b">
         <v>0</v>
       </c>
       <c r="AE21" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG21" t="b">
         <v>0</v>
@@ -2910,7 +2910,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>132793557</v>
+        <v>132793034</v>
       </c>
       <c r="B22" t="n">
         <v>57958</v>
@@ -2950,10 +2950,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>497804</v>
+        <v>497860</v>
       </c>
       <c r="R22" t="n">
-        <v>6666386</v>
+        <v>6666362</v>
       </c>
       <c r="S22" t="n">
         <v>1</v>
@@ -2985,7 +2985,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>10:18</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2995,14 +2995,14 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>10:18</t>
         </is>
       </c>
       <c r="AD22" t="b">
         <v>0</v>
       </c>
       <c r="AE22" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG22" t="b">
         <v>0</v>

--- a/artfynd/A 58513-2025 artfynd.xlsx
+++ b/artfynd/A 58513-2025 artfynd.xlsx
@@ -2574,10 +2574,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>132793510</v>
+        <v>132792291</v>
       </c>
       <c r="B19" t="n">
-        <v>57958</v>
+        <v>57955</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2585,16 +2585,16 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -2614,13 +2614,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>497770</v>
+        <v>497918</v>
       </c>
       <c r="R19" t="n">
-        <v>6666395</v>
+        <v>6666359</v>
       </c>
       <c r="S19" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2649,7 +2649,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2659,7 +2659,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2686,10 +2686,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>132792291</v>
+        <v>132793510</v>
       </c>
       <c r="B20" t="n">
-        <v>57955</v>
+        <v>57958</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2697,16 +2697,16 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -2726,13 +2726,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>497918</v>
+        <v>497770</v>
       </c>
       <c r="R20" t="n">
-        <v>6666359</v>
+        <v>6666395</v>
       </c>
       <c r="S20" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2761,7 +2761,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2771,7 +2771,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AD20" t="b">

--- a/artfynd/A 58513-2025 artfynd.xlsx
+++ b/artfynd/A 58513-2025 artfynd.xlsx
@@ -2574,10 +2574,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>132792291</v>
+        <v>132793510</v>
       </c>
       <c r="B19" t="n">
-        <v>57955</v>
+        <v>57958</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2585,16 +2585,16 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -2614,13 +2614,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>497918</v>
+        <v>497770</v>
       </c>
       <c r="R19" t="n">
-        <v>6666359</v>
+        <v>6666395</v>
       </c>
       <c r="S19" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2649,7 +2649,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2659,7 +2659,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2686,10 +2686,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>132793510</v>
+        <v>132792291</v>
       </c>
       <c r="B20" t="n">
-        <v>57958</v>
+        <v>57955</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2697,16 +2697,16 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -2726,13 +2726,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>497770</v>
+        <v>497918</v>
       </c>
       <c r="R20" t="n">
-        <v>6666395</v>
+        <v>6666359</v>
       </c>
       <c r="S20" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2761,7 +2761,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2771,7 +2771,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="AD20" t="b">

--- a/artfynd/A 58513-2025 artfynd.xlsx
+++ b/artfynd/A 58513-2025 artfynd.xlsx
@@ -1347,50 +1347,45 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>132795456</v>
+        <v>132792240</v>
       </c>
       <c r="B8" t="n">
-        <v>57955</v>
+        <v>91291</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100049</v>
+        <v>5685</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Gullgröppa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Pseudomerulius aureus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Jülich</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Saxberget, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>497730</v>
+        <v>497881</v>
       </c>
       <c r="R8" t="n">
-        <v>6666268</v>
+        <v>6666310</v>
       </c>
       <c r="S8" t="n">
         <v>1</v>
@@ -1422,7 +1417,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1432,7 +1427,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1459,45 +1454,50 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>132792240</v>
+        <v>132795456</v>
       </c>
       <c r="B9" t="n">
-        <v>91291</v>
+        <v>57955</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5685</v>
+        <v>100049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Gullgröppa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Pseudomerulius aureus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Jülich</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Saxberget, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>497881</v>
+        <v>497730</v>
       </c>
       <c r="R9" t="n">
-        <v>6666310</v>
+        <v>6666268</v>
       </c>
       <c r="S9" t="n">
         <v>1</v>
@@ -1529,7 +1529,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1539,7 +1539,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -2574,10 +2574,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>132793510</v>
+        <v>132792291</v>
       </c>
       <c r="B19" t="n">
-        <v>57958</v>
+        <v>57955</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2585,16 +2585,16 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -2614,13 +2614,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>497770</v>
+        <v>497918</v>
       </c>
       <c r="R19" t="n">
-        <v>6666395</v>
+        <v>6666359</v>
       </c>
       <c r="S19" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2649,7 +2649,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2659,7 +2659,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2686,10 +2686,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>132792291</v>
+        <v>132793510</v>
       </c>
       <c r="B20" t="n">
-        <v>57955</v>
+        <v>57958</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2697,16 +2697,16 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -2726,13 +2726,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>497918</v>
+        <v>497770</v>
       </c>
       <c r="R20" t="n">
-        <v>6666359</v>
+        <v>6666395</v>
       </c>
       <c r="S20" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2761,7 +2761,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2771,7 +2771,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AD20" t="b">

--- a/artfynd/A 58513-2025 artfynd.xlsx
+++ b/artfynd/A 58513-2025 artfynd.xlsx
@@ -675,50 +675,45 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>132795914</v>
+        <v>132792240</v>
       </c>
       <c r="B2" t="n">
-        <v>57958</v>
+        <v>91347</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>5685</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gullgröppa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pseudomerulius aureus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Jülich</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Saxberget, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>497639</v>
+        <v>497881</v>
       </c>
       <c r="R2" t="n">
-        <v>6666288</v>
+        <v>6666310</v>
       </c>
       <c r="S2" t="n">
         <v>1</v>
@@ -750,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,50 +782,45 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>132795817</v>
+        <v>132795978</v>
       </c>
       <c r="B3" t="n">
-        <v>57955</v>
+        <v>79373</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Saxberget, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>497613</v>
+        <v>497639</v>
       </c>
       <c r="R3" t="n">
-        <v>6666353</v>
+        <v>6666288</v>
       </c>
       <c r="S3" t="n">
         <v>1</v>
@@ -862,7 +852,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +862,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,48 +889,53 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>132795978</v>
+        <v>132791703</v>
       </c>
       <c r="B4" t="n">
-        <v>79333</v>
+        <v>57972</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Saxberget, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>497639</v>
+        <v>497778</v>
       </c>
       <c r="R4" t="n">
-        <v>6666288</v>
+        <v>6666268</v>
       </c>
       <c r="S4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -969,7 +964,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:35</t>
+          <t>09:37</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -979,7 +974,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:35</t>
+          <t>09:37</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1006,14 +1001,14 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>132792368</v>
+        <v>132792291</v>
       </c>
       <c r="B5" t="n">
-        <v>57955</v>
+        <v>57972</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
@@ -1037,7 +1032,7 @@
       <c r="I5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1046,13 +1041,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>497892</v>
+        <v>497918</v>
       </c>
       <c r="R5" t="n">
-        <v>6666338</v>
+        <v>6666359</v>
       </c>
       <c r="S5" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1081,7 +1076,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1091,7 +1086,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1118,14 +1113,14 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>132794932</v>
+        <v>132792333</v>
       </c>
       <c r="B6" t="n">
-        <v>57955</v>
+        <v>57972</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
@@ -1149,7 +1144,7 @@
       <c r="I6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>bobygge</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1158,10 +1153,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>497782</v>
+        <v>497895</v>
       </c>
       <c r="R6" t="n">
-        <v>6666331</v>
+        <v>6666323</v>
       </c>
       <c r="S6" t="n">
         <v>1</v>
@@ -1193,7 +1188,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>09:53</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1203,12 +1198,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>11:02</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Färskt</t>
+          <t>09:53</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1235,27 +1225,27 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>132793317</v>
+        <v>132792368</v>
       </c>
       <c r="B7" t="n">
-        <v>57958</v>
+        <v>57972</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1275,10 +1265,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>497841</v>
+        <v>497892</v>
       </c>
       <c r="R7" t="n">
-        <v>6666362</v>
+        <v>6666338</v>
       </c>
       <c r="S7" t="n">
         <v>1</v>
@@ -1310,7 +1300,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1320,14 +1310,14 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
       <c r="AE7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG7" t="b">
         <v>0</v>
@@ -1347,10 +1337,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>132792240</v>
+        <v>132792533</v>
       </c>
       <c r="B8" t="n">
-        <v>91291</v>
+        <v>57972</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1358,34 +1348,39 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5685</v>
+        <v>100049</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Gullgröppa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Pseudomerulius aureus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Jülich</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Saxberget, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>497881</v>
+        <v>497914</v>
       </c>
       <c r="R8" t="n">
-        <v>6666310</v>
+        <v>6666329</v>
       </c>
       <c r="S8" t="n">
         <v>1</v>
@@ -1417,7 +1412,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>10:02</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1427,7 +1422,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>10:02</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1454,14 +1449,14 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>132795456</v>
+        <v>132792691</v>
       </c>
       <c r="B9" t="n">
-        <v>57955</v>
+        <v>57972</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
@@ -1485,7 +1480,7 @@
       <c r="I9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>besöker bebott bo</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1494,10 +1489,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>497730</v>
+        <v>497882</v>
       </c>
       <c r="R9" t="n">
-        <v>6666268</v>
+        <v>6666359</v>
       </c>
       <c r="S9" t="n">
         <v>1</v>
@@ -1529,7 +1524,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>10:07</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1539,7 +1534,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>10:07</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1566,14 +1561,14 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>132791703</v>
+        <v>132794021</v>
       </c>
       <c r="B10" t="n">
-        <v>57955</v>
+        <v>57972</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
@@ -1606,13 +1601,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>497778</v>
+        <v>497625</v>
       </c>
       <c r="R10" t="n">
-        <v>6666268</v>
+        <v>6666407</v>
       </c>
       <c r="S10" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1641,7 +1636,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>09:37</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1651,7 +1646,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>09:37</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1678,14 +1673,14 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>132792533</v>
+        <v>132794362</v>
       </c>
       <c r="B11" t="n">
-        <v>57955</v>
+        <v>57972</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
@@ -1709,7 +1704,7 @@
       <c r="I11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1718,10 +1713,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>497914</v>
+        <v>497703</v>
       </c>
       <c r="R11" t="n">
-        <v>6666329</v>
+        <v>6666468</v>
       </c>
       <c r="S11" t="n">
         <v>1</v>
@@ -1753,7 +1748,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>10:02</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1763,7 +1758,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>10:02</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1790,27 +1785,27 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>132792911</v>
+        <v>132794932</v>
       </c>
       <c r="B12" t="n">
-        <v>57958</v>
+        <v>57972</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1821,7 +1816,7 @@
       <c r="I12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>bobygge</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -1830,10 +1825,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>497882</v>
+        <v>497782</v>
       </c>
       <c r="R12" t="n">
-        <v>6666359</v>
+        <v>6666331</v>
       </c>
       <c r="S12" t="n">
         <v>1</v>
@@ -1865,7 +1860,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1875,14 +1870,19 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>11:02</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Färskt</t>
         </is>
       </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
       <c r="AE12" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG12" t="b">
         <v>0</v>
@@ -1902,14 +1902,14 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>132792691</v>
+        <v>132795456</v>
       </c>
       <c r="B13" t="n">
-        <v>57955</v>
+        <v>57972</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
@@ -1933,7 +1933,7 @@
       <c r="I13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
-          <t>besöker bebott bo</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -1942,10 +1942,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>497882</v>
+        <v>497730</v>
       </c>
       <c r="R13" t="n">
-        <v>6666359</v>
+        <v>6666268</v>
       </c>
       <c r="S13" t="n">
         <v>1</v>
@@ -1977,7 +1977,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>10:07</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1987,7 +1987,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>10:07</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2014,14 +2014,14 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>132794362</v>
+        <v>132795817</v>
       </c>
       <c r="B14" t="n">
-        <v>57955</v>
+        <v>57972</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
@@ -2045,7 +2045,7 @@
       <c r="I14" t="inlineStr"/>
       <c r="M14" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -2054,10 +2054,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>497703</v>
+        <v>497613</v>
       </c>
       <c r="R14" t="n">
-        <v>6666468</v>
+        <v>6666353</v>
       </c>
       <c r="S14" t="n">
         <v>1</v>
@@ -2089,7 +2089,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2099,7 +2099,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2126,10 +2126,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>132795695</v>
+        <v>132792911</v>
       </c>
       <c r="B15" t="n">
-        <v>57958</v>
+        <v>57975</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2157,7 +2157,7 @@
       <c r="I15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -2166,10 +2166,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>497634</v>
+        <v>497882</v>
       </c>
       <c r="R15" t="n">
-        <v>6666312</v>
+        <v>6666359</v>
       </c>
       <c r="S15" t="n">
         <v>1</v>
@@ -2201,7 +2201,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2211,14 +2211,14 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
       <c r="AE15" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG15" t="b">
         <v>0</v>
@@ -2238,10 +2238,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>132792333</v>
+        <v>132793034</v>
       </c>
       <c r="B16" t="n">
-        <v>57955</v>
+        <v>57975</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2249,16 +2249,16 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -2278,10 +2278,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>497895</v>
+        <v>497860</v>
       </c>
       <c r="R16" t="n">
-        <v>6666323</v>
+        <v>6666362</v>
       </c>
       <c r="S16" t="n">
         <v>1</v>
@@ -2313,7 +2313,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>09:53</t>
+          <t>10:18</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2323,7 +2323,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>09:53</t>
+          <t>10:18</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2350,10 +2350,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>132794021</v>
+        <v>132793317</v>
       </c>
       <c r="B17" t="n">
-        <v>57955</v>
+        <v>57975</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2361,16 +2361,16 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -2381,7 +2381,7 @@
       <c r="I17" t="inlineStr"/>
       <c r="M17" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -2390,13 +2390,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>497625</v>
+        <v>497841</v>
       </c>
       <c r="R17" t="n">
-        <v>6666407</v>
+        <v>6666362</v>
       </c>
       <c r="S17" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2425,7 +2425,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2435,14 +2435,14 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
       <c r="AE17" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG17" t="b">
         <v>0</v>
@@ -2462,10 +2462,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>132793781</v>
+        <v>132793510</v>
       </c>
       <c r="B18" t="n">
-        <v>57958</v>
+        <v>57975</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2502,10 +2502,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>497788</v>
+        <v>497770</v>
       </c>
       <c r="R18" t="n">
-        <v>6666403</v>
+        <v>6666395</v>
       </c>
       <c r="S18" t="n">
         <v>1</v>
@@ -2537,7 +2537,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>10:33</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2547,7 +2547,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>10:33</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2574,10 +2574,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>132792291</v>
+        <v>132793557</v>
       </c>
       <c r="B19" t="n">
-        <v>57955</v>
+        <v>57975</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2585,16 +2585,16 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -2605,7 +2605,7 @@
       <c r="I19" t="inlineStr"/>
       <c r="M19" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
@@ -2614,13 +2614,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>497918</v>
+        <v>497804</v>
       </c>
       <c r="R19" t="n">
-        <v>6666359</v>
+        <v>6666386</v>
       </c>
       <c r="S19" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2649,7 +2649,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2659,14 +2659,14 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
       <c r="AE19" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG19" t="b">
         <v>0</v>
@@ -2686,10 +2686,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>132793510</v>
+        <v>132793781</v>
       </c>
       <c r="B20" t="n">
-        <v>57958</v>
+        <v>57975</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2726,10 +2726,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>497770</v>
+        <v>497788</v>
       </c>
       <c r="R20" t="n">
-        <v>6666395</v>
+        <v>6666403</v>
       </c>
       <c r="S20" t="n">
         <v>1</v>
@@ -2761,7 +2761,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>10:33</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2771,7 +2771,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>10:33</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2798,10 +2798,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>132793557</v>
+        <v>132794847</v>
       </c>
       <c r="B21" t="n">
-        <v>57958</v>
+        <v>57975</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2838,10 +2838,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>497804</v>
+        <v>497782</v>
       </c>
       <c r="R21" t="n">
-        <v>6666386</v>
+        <v>6666331</v>
       </c>
       <c r="S21" t="n">
         <v>1</v>
@@ -2873,7 +2873,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2883,14 +2883,14 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AD21" t="b">
         <v>0</v>
       </c>
       <c r="AE21" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG21" t="b">
         <v>0</v>
@@ -2910,10 +2910,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>132793034</v>
+        <v>132795352</v>
       </c>
       <c r="B22" t="n">
-        <v>57958</v>
+        <v>57975</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2941,7 +2941,7 @@
       <c r="I22" t="inlineStr"/>
       <c r="M22" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
@@ -2950,10 +2950,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>497860</v>
+        <v>497730</v>
       </c>
       <c r="R22" t="n">
-        <v>6666362</v>
+        <v>6666268</v>
       </c>
       <c r="S22" t="n">
         <v>1</v>
@@ -2985,7 +2985,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>10:18</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2995,7 +2995,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>10:18</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3022,10 +3022,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>132794847</v>
+        <v>132795695</v>
       </c>
       <c r="B23" t="n">
-        <v>57958</v>
+        <v>57975</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3053,7 +3053,7 @@
       <c r="I23" t="inlineStr"/>
       <c r="M23" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
@@ -3062,10 +3062,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>497782</v>
+        <v>497634</v>
       </c>
       <c r="R23" t="n">
-        <v>6666331</v>
+        <v>6666312</v>
       </c>
       <c r="S23" t="n">
         <v>1</v>
@@ -3097,7 +3097,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3107,7 +3107,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3134,10 +3134,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>132795352</v>
+        <v>132795914</v>
       </c>
       <c r="B24" t="n">
-        <v>57958</v>
+        <v>57975</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3165,7 +3165,7 @@
       <c r="I24" t="inlineStr"/>
       <c r="M24" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
@@ -3174,10 +3174,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>497730</v>
+        <v>497639</v>
       </c>
       <c r="R24" t="n">
-        <v>6666268</v>
+        <v>6666288</v>
       </c>
       <c r="S24" t="n">
         <v>1</v>
@@ -3209,7 +3209,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3219,7 +3219,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AD24" t="b">
